--- a/WorkBot/main/data/orders/Palmer/Palmer_Bakery_20260826.xlsx
+++ b/WorkBot/main/data/orders/Palmer/Palmer_Bakery_20260826.xlsx
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>72.5</v>
       </c>
       <c r="E6" t="n">
-        <v>72.5</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="7">
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>72.5</v>
       </c>
       <c r="E7" t="n">
-        <v>580</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
